--- a/content/templates/files/conversation-tracker/127-conversation-tracker-example.xlsx
+++ b/content/templates/files/conversation-tracker/127-conversation-tracker-example.xlsx
@@ -678,7 +678,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Track the 20 people you message to land 10 real customer conversations, with follow-up dates and the facts that matter from each call.</t>
+          <t>Track the 20 people you message and every conversation you have, with follow-up dates and the facts that matter from each call.</t>
         </is>
       </c>
     </row>
